--- a/themes/contract.xlsx
+++ b/themes/contract.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,101 +450,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debet: Получить копию договора по вкладу, счету или дебетовой карте можно в [офисе банка]({{$temp.officeLink}})  </t>
+          <t>MKK:  Получить кредитный договор можно в личном кабинете. Войти в личный кабинет можно через [сайт](https://uralsibfinance.ru/) раздел «Личный кабинет».</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debet: Получить копию договора по вкладу, счету или дебетовой карте можно в [офисе банка]({{$temp.officeLink}}).  </t>
+          <t>MKK:  Получить кредитный договор можно в личном кабинете. Войти в личный кабинет можно через [сайт](https://uralsibfinance.ru/), раздел «Личный кабинет».</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Для получения копии договора по кредитной карте напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)'</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Для получения копии договора по кредитной карте напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).'</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Для получения копии договора по кредитам, выданным в магазине на товары напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)'</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Для получения копии договора по кредитам, выданным в магазине на товары напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).'</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MKK:  Получить кредитный договор можно в личном кабинете. Войти в личный кабинет можно через [сайт](https://uralsibfinance.ru/) раздел «Личный кабинет».</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MKK:  Получить кредитный договор можно в личном кабинете. Войти в личный кабинет можно через [сайт](https://uralsibfinance.ru/), раздел «Личный кабинет».</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>добавлена запятая перед уточняющим «раздел «Личный кабинет»»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other: Получить копию договора по потребительскому кредиту, автокредиту и ипотеке можно только в [офисе банка]({{$temp.officeLink}})  </t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other: Получить копию договора по потребительскому кредиту, автокредиту и ипотеке можно только в [офисе банка]({{$temp.officeLink}}).  </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
